--- a/r4-core-94-gemeindecode-austrian-address/all-profiles.xlsx
+++ b/r4-core-94-gemeindecode-austrian-address/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T11:20:43+00:00</t>
+    <t>2024-10-25T11:59:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-94-gemeindecode-austrian-address/all-profiles.xlsx
+++ b/r4-core-94-gemeindecode-austrian-address/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T11:59:01+00:00</t>
+    <t>2024-10-26T14:00:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -16483,7 +16483,7 @@
         <v>76</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>23</v>
